--- a/docs/data/jp/xlsx/6701.xlsx
+++ b/docs/data/jp/xlsx/6701.xlsx
@@ -1130,7 +1130,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IT서비스</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1388,7 +1388,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>사회 인프라</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -6110,7 +6110,7 @@
     <row r="88">
       <c r="A88" s="18" t="inlineStr">
         <is>
-          <t>Finance Income Ope CF</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
@@ -6239,7 +6239,7 @@
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>Decrease Increase In Trade And Other Receivables Ope CF</t>
+          <t>매출채권 및 기타채권 증감액</t>
         </is>
       </c>
       <c r="F91" s="20" t="n">
@@ -6378,7 +6378,7 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Trade And Other Payables Ope CF</t>
+          <t>매입채무 및 기타채무 증감액</t>
         </is>
       </c>
       <c r="F95" s="20" t="n">
@@ -6474,7 +6474,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Increase Or Decrease In Retirement Benefit Asset Or Liability Ope CF</t>
+          <t>퇴직급여 부채·자산 증감액</t>
         </is>
       </c>
       <c r="J98" s="20" t="n">
@@ -6632,7 +6632,7 @@
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>Dividends Received Ope CF</t>
+          <t>배당금 수취액</t>
         </is>
       </c>
       <c r="F103" s="20" t="n">
@@ -6934,7 +6934,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Purchase Of Equity Instruments Measured At Fair Value Through Other Comprehensive Income Inv CFIFRS</t>
+          <t>기타포괄손익-공정가치 지분상품 취득 지출</t>
         </is>
       </c>
       <c r="P111" s="20" t="n">
@@ -6960,7 +6960,7 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Equity Instruments Measured At Fair Value Through Other Comprehensive Income Inv CFIFRS</t>
+          <t>기타포괄손익-공정가치 지분상품 매각 수입</t>
         </is>
       </c>
       <c r="P113" s="20" t="n">
@@ -6973,7 +6973,7 @@
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>Purchase Of Equity Instruments Measured At Fair Value Through Other Comprehensive Income Inv CF</t>
+          <t>기타포괄손익-공정가치 지분상품 취득 지출</t>
         </is>
       </c>
       <c r="F114" s="20" t="n">
@@ -7013,7 +7013,7 @@
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sales Of Equity Instruments Measured At Fair Value Through Other Comprehensive Income Inv CF</t>
+          <t>기타포괄손익-공정가치 지분상품 매각 수입</t>
         </is>
       </c>
       <c r="F115" s="20" t="n">
@@ -7096,7 +7096,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Acquisition Of Subsidiaries Net Of Cash Acquired Inv CF</t>
+          <t>자회사 취득 수입</t>
         </is>
       </c>
       <c r="P117" s="20" t="n">
@@ -7109,7 +7109,7 @@
     <row r="118">
       <c r="A118" s="18" t="inlineStr">
         <is>
-          <t>Acquisition Of Subsidiaries Net Of Cash Acquired IFRSInv CF</t>
+          <t>자회사 취득 수입</t>
         </is>
       </c>
       <c r="Q118" s="20" t="n">
@@ -7128,7 +7128,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Subsidiaries Inv CF</t>
+          <t>자회사 매각 수입</t>
         </is>
       </c>
       <c r="F119" s="20" t="n">
@@ -7171,7 +7171,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Payments For Sale Of Subsidiaries Inv CF</t>
+          <t>자회사 매각 지출</t>
         </is>
       </c>
       <c r="F120" s="20" t="n">
@@ -7211,7 +7211,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Purchase Of Investments Accounted For Using Equity Method Inv CF</t>
+          <t>관계·공동기업 투자 취득 지출</t>
         </is>
       </c>
       <c r="F121" s="20" t="n">
@@ -7254,7 +7254,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Investments Accounted For Using Equity Method Inv CF</t>
+          <t>관계·공동기업 투자 매각 수입</t>
         </is>
       </c>
       <c r="F122" s="20" t="n">
@@ -7670,7 +7670,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Changes In Ownership Interests In Subsidiaries That Do Not Result In Loss Of Control Fin CF</t>
+          <t>비지배지분에 자회사 지분 매각 수입</t>
         </is>
       </c>
       <c r="P133" s="20" t="n">
@@ -7692,7 +7692,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>Payments For Acquisition Of Interests In Subsidiaries From Non Controlling Interests Fin CF</t>
+          <t>비지배지분으로부터 자회사 지분 취득 지출</t>
         </is>
       </c>
       <c r="F134" s="20" t="n">
@@ -7760,7 +7760,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>Dividends Paid To Non Controlling Interests Fin CF</t>
+          <t>비지배지분 배당금 지급액</t>
         </is>
       </c>
       <c r="F136" s="20" t="n">
@@ -7847,7 +7847,7 @@
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Issuance Of Preference Shares With Put Call Options Fin CF</t>
+          <t>상환옵션부 우선주 발행 수입</t>
         </is>
       </c>
       <c r="F139" s="20" t="n">
@@ -7986,7 +7986,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>Effect Of Exchange Rate Changes On Cash And Cash Equivalents</t>
+          <t>현금성자산 환율변동 효과</t>
         </is>
       </c>
       <c r="F143" s="20" t="n">
@@ -8072,7 +8072,7 @@
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>Decrease In Cash And Cash Equivalents Resulting From Transfer To Assets Held For Sale CF</t>
+          <t>매각예정자산 대체에 따른 현금성자산 증감액</t>
         </is>
       </c>
       <c r="P145" s="20" t="n">
@@ -8085,7 +8085,7 @@
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>Decrease In Cash And Cash Equivalents Resulting From CF</t>
+          <t>매각예정자산 대체에 따른 현금성자산 증감액</t>
         </is>
       </c>
       <c r="Q146" s="20" t="n">
@@ -10996,7 +10996,7 @@
     <row r="80">
       <c r="A80" s="18" t="inlineStr">
         <is>
-          <t>Property Plant And Equipment</t>
+          <t>유형자산(순액)</t>
         </is>
       </c>
       <c r="C80" s="20" t="n">
@@ -11052,7 +11052,7 @@
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>무형자산(순액)</t>
         </is>
       </c>
       <c r="C82" s="20" t="n">
@@ -11304,7 +11304,7 @@
     <row r="91">
       <c r="A91" s="18" t="inlineStr">
         <is>
-          <t>Bonds And Borrowings CL</t>
+          <t>사채 및 차입금</t>
         </is>
       </c>
       <c r="C91" s="20" t="n">
@@ -11572,7 +11572,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Bonds And Borrowings NCL</t>
+          <t>사채 및 차입금</t>
         </is>
       </c>
       <c r="C101" s="20" t="n">
